--- a/driving-situation-alert/tmp/submission/excel/submission_all_in_one.xlsx
+++ b/driving-situation-alert/tmp/submission/excel/submission_all_in_one.xlsx
@@ -20,7 +20,6 @@
     <sheet name="05_Unit_Test" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="06_Integration_Test" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="07_System_Test" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="README_SUBMISSION_DOCSET" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1121,14 +1120,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
     <col width="56" customWidth="1" min="3" max="3"/>
     <col width="66" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1922,7 +1923,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>인터페이스 요약 (SWE.3 BP2 축소본)</t>
+          <t>대표 구현 추적 (제출 보강)</t>
         </is>
       </c>
     </row>
@@ -1930,133 +1931,402 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>인터페이스</t>
+          <t>Req ID</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>Func ID</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>Flow/Comm</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>타이밍</t>
+          <t>핵심 Var</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>구현 파일</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Code Ref</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>검증 링크</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>CAN Ingestion</t>
+          <t>Req_001</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>도메인 CAN 프레임</t>
+          <t>Func_001</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>정규화 Core 변수</t>
+          <t>Flow_001 / Comm_001</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>vehicleSpeedNorm, driveStateNorm</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>invalid 값 필터링</t>
+          <t>`canoe/src/capl/logic/ADAS_WARN_CTRL.can`</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>MOD_01.F001</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>UT_ADAS_001</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>ETH Core Link</t>
+          <t>Req_017</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>ETH 논리 계약(E100/E200/E213~E216)</t>
+          <t>Func_017</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>중재/상태 변수</t>
+          <t>Flow_004 / Comm_004</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>50~100ms + Event</t>
+          <t>emergencyType, eta, emergencyDirection</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>CANoe.CAN 환경은 stub 대체</t>
+          <t>`canoe/src/capl/ems/EMS_POLICE_TX.can`</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>MOD_03.F017</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>UT_EMS_POL_001</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Output Dispatch</t>
+          <t>Req_022</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>selectedAlertLevel/Type</t>
+          <t>Func_022</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Ambient/Cluster CAN 출력</t>
+          <t>Flow_006 / Comm_006</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>50ms</t>
+          <t>emergencyContext, selectedAlertLevel</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>timeoutClear/failSafeMode 반영</t>
+          <t>`canoe/src/capl/logic/WARN_ARB_MGR.can`</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>MOD_06.F022</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>UT_ARB_001</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
+          <t>Req_035</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Func_035</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Flow_007 / Comm_007</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>selectedAlertType, ambientColor</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>`canoe/src/capl/output/AMBIENT_CTRL.can`</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>MOD_11.F035</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>UT_BCM_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Req_120</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Func_120</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Flow_120 / Comm_120</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>proximityRiskLevel</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>`canoe/src/capl/logic/ADAS_WARN_CTRL.can`</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>MOD_01.F120</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>UT_V2_RISK_001 / IT_V2_RISK_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Req_130</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Func_130</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Flow_130 / Comm_130</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>objectTrackValid, objectRange, objectRelSpeed</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>`canoe/src/capl/logic/ADAS_WARN_CTRL.can`</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>MOD_01.F130</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>UT_ADAS_OBJ_RISK_001 (Planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>인터페이스 요약 (SWE.3 BP2 축소본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>인터페이스</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>출력</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>타이밍</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>CAN Ingestion</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>도메인 CAN 프레임</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>정규화 Core 변수</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>invalid 값 필터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>ETH Core Link</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>ETH 논리 계약(E100/E200/E213~E216)</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>중재/상태 변수</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>50~100ms + Event</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>CANoe.CAN 환경은 stub 대체</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Output Dispatch</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>selectedAlertLevel/Type</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Ambient/Cluster CAN 출력</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>50ms</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>timeoutClear/failSafeMode 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
           <t>Validation Harness</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>testScenario/sysvar 입력</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>scenarioResult/log</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E100" s="4" t="inlineStr">
         <is>
           <t>양산 경로와 분리</t>
         </is>
@@ -7309,235 +7579,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="76" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>제출용 축소본 인덱스 (00 통합 2문서 확정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>- 생성 위치: driving-situation-alert/tmp/submission/docs/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>- 생성 기준: tmp/submission/REDUCTION_SCOPE_00_TO_07_FOR_EXCEL.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>1) 제출 본편 (권장)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>- 00_MASTER_Project_Framework.md  &lt;!-- 00 + 00b 통합 --&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>- 00_MASTER_Governance_Summary.md  &lt;!-- 00c + 00d + 00e + 00f + 00g 통합 --&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>- 01_Requirements.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>- 02_Concept_design.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>- 03_Function_definition.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>- 0301_SysFuncAnalysis.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>- 0302_NWflowDef.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>- 0303_Communication_Specification.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>- 0304_System_Variables.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>- 04_SW_Implementation.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>- 05_Unit_Test.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>- 06_Integration_Test.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>- 07_System_Test.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2) 부록/내부 참조 (요청 시 추가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>- 위치: tmp/submission/docs/governance/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>- governance/00_VModel_Mapping.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>- governance/00b_Project_Scope.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>- governance/00c_Req_Classification_and_Safety_Profile.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>- governance/00d_HARA_Worksheet.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>- governance/00e_ECU_Naming_Standard.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>- governance/00f_CAN_ID_Allocation_Standard.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>- governance/00g_RTE_Name_Mapping_Standard.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>3) 제출 제외</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>- 00a_Audit_Readiness_Checklist.md (내부 운영 체크리스트)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>- 00e_ID_Naming_and_CAN_ID_Standard.md (분리 안내 인덱스 성격)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7947,11 +7988,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H308"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="71" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -11349,7 +11390,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>정책표와 일치</t>
+          <t>03 경고 표시 정책표와 일치</t>
         </is>
       </c>
     </row>
@@ -12213,7 +12254,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>표시 정책표(색+패턴) 일치</t>
+          <t>03 경고 표시 정책표(색+패턴) 일치</t>
         </is>
       </c>
     </row>
@@ -12277,7 +12318,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>구간별 고정 패턴 정책표 일치</t>
+          <t>03 경고 표시 정책표(구간 패턴) 일치</t>
         </is>
       </c>
     </row>
@@ -14048,87 +14089,39 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>B. Part별 요구사항</t>
+          <t>A-3. 경고 표시 정책 참조 (요약)</t>
         </is>
       </c>
     </row>
     <row r="223"/>
     <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>Part 0. 차량 기본 기능 요구사항 (Req_101~Req_107, Req_109, Req_113, Req_116, Req_118~Req_119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="225"/>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>- Req_008, Req_035, Req_037의 색상/패턴/코드 매핑 상세는 03_Function_definition.md의 경고 표시 정책표를 단일 기준으로 사용한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>- 본 문서(01)는 VC 기준과 수용 문구만 유지하고, 정책값 자체는 03에서 관리한다.</t>
+        </is>
+      </c>
+    </row>
     <row r="226">
-      <c r="A226" s="3" t="inlineStr">
-        <is>
-          <t>Req. ID</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="C226" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>중요도/긴급도</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>요청자</t>
-        </is>
-      </c>
-      <c r="F226" s="3" t="inlineStr">
-        <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="G226" s="3" t="inlineStr">
-        <is>
-          <t>변경사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>Req_101~Req_107, Req_109, Req_113, Req_116, Req_118~Req_119</t>
-        </is>
-      </c>
-      <c r="B227" s="4" t="inlineStr">
-        <is>
-          <t>차량 베이스 기능 요구</t>
-        </is>
-      </c>
-      <c r="C227" s="4" t="inlineStr">
-        <is>
-          <t>시동/기어/입력/표시와 실내편의(공조/시트/미러), 차체연동(도어/와이퍼·우적), 보안/오디오 상태 반영</t>
-        </is>
-      </c>
-      <c r="D227" s="4" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="E227" s="4" t="inlineStr"/>
-      <c r="F227" s="4" t="inlineStr"/>
-      <c r="G227" s="4" t="inlineStr"/>
-    </row>
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>- 05/06/07 테스트 문서는 03 정책표 기준 검증 문구로 정합을 맞춘다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227"/>
     <row r="228"/>
     <row r="229"/>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Part 1. 공통 베이스 요구사항 (Req_001~Req_006)</t>
+          <t>B. Part별 요구사항 (제출 요약)</t>
         </is>
       </c>
     </row>
@@ -14136,845 +14129,250 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>Req. ID</t>
+          <t>Part</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>요약</t>
+          <t>Req 범위</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D232" s="3" t="inlineStr">
-        <is>
-          <t>중요도/긴급도</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="inlineStr">
-        <is>
-          <t>요청자</t>
-        </is>
-      </c>
-      <c r="F232" s="3" t="inlineStr">
-        <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="G232" s="3" t="inlineStr">
-        <is>
-          <t>변경사항</t>
+          <t>제출 목적</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>Req_001~Req_006</t>
+          <t>Part 0</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>공통 경고 엔진 요구</t>
+          <t>Req_101~107, 109, 113, 116, 118~119</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>경고 시작/해제/원인 표시/반복 억제 등 공통 경고 동작</t>
-        </is>
-      </c>
-      <c r="D233" s="4" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="E233" s="4" t="inlineStr"/>
-      <c r="F233" s="4" t="inlineStr"/>
-      <c r="G233" s="4" t="inlineStr"/>
-    </row>
-    <row r="234"/>
-    <row r="235"/>
+          <t>차량 기본 기능(입력/표시/상태)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>Part 1</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>Req_001~006</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>공통 경고 엔진(활성/해제/중복억제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>Part 2</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>Req_007~016</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>구간 인식(스쿨존/고속도로/유도)</t>
+        </is>
+      </c>
+    </row>
     <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>Part 2. 구간 인식 요구사항 (Req_007~Req_016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="237"/>
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>Part 3</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>Req_017, 019~026</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>긴급차량 접근 경고</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>Part 4</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>Req_027~034</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>경보 우선순위 판정/전환 안정화</t>
+        </is>
+      </c>
+    </row>
     <row r="238">
-      <c r="A238" s="3" t="inlineStr">
-        <is>
-          <t>Req. ID</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="C238" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D238" s="3" t="inlineStr">
-        <is>
-          <t>중요도/긴급도</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>요청자</t>
-        </is>
-      </c>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="G238" s="3" t="inlineStr">
-        <is>
-          <t>변경사항</t>
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>Part 5</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>Req_035, 037, 040</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>표시 정책(색/패턴/문구)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>Req_007~Req_016</t>
+          <t>Part 6</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>구간 시나리오 요구</t>
+          <t>Req_041~043, 110~112</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>일반/스쿨존/고속도로/유도 구간 경고 및 전환/복귀 동작</t>
-        </is>
-      </c>
-      <c r="D239" s="4" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="E239" s="4" t="inlineStr"/>
-      <c r="F239" s="4" t="inlineStr"/>
-      <c r="G239" s="4" t="inlineStr"/>
-    </row>
-    <row r="240"/>
-    <row r="241"/>
+          <t>검증/인수 조건(SIL 실행 환경)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>Part 7</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>Req_120~121, 123, 125~129, 130~139</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>V2 + ADAS 확장</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>Part 8</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>Req_018, 036, 038, 039, 108, 114, 115, 117, 122, 124</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>Legacy 매핑 관리</t>
+        </is>
+      </c>
+    </row>
     <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>Part 3. 긴급차량 경고 요구사항 (Req_017, Req_019~Req_026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="243"/>
-    <row r="244">
-      <c r="A244" s="3" t="inlineStr">
-        <is>
-          <t>Req. ID</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="C244" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>중요도/긴급도</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>요청자</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="inlineStr">
-        <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="G244" s="3" t="inlineStr">
-        <is>
-          <t>변경사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="4" t="inlineStr">
-        <is>
-          <t>Req_017, Req_019~Req_026</t>
-        </is>
-      </c>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>긴급차량 시나리오 요구</t>
-        </is>
-      </c>
-      <c r="C245" s="4" t="inlineStr">
-        <is>
-          <t>긴급차량 접근 경고, 종류/방향 표시, 종료/중복 처리</t>
-        </is>
-      </c>
-      <c r="D245" s="4" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="E245" s="4" t="inlineStr"/>
-      <c r="F245" s="4" t="inlineStr"/>
-      <c r="G245" s="4" t="inlineStr"/>
-    </row>
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>Part 9</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>Req_140~147</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>차량 경보 편의 확장(Pre-Activation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>Part 10</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>Req_148~155</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>경고 강건성·인지성 확장(Pre-Activation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244"/>
+    <row r="245"/>
     <row r="246"/>
-    <row r="247"/>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>Part 4. 중재(우선순위/충돌해결) 요구사항 (Req_027~Req_034)</t>
-        </is>
-      </c>
-    </row>
-    <row r="249"/>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>요구사항 사용 가이드 (제출 요약)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248"/>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>- 대외 설명은 상단 통합 기본요구사항 표를 기준으로 사용한다.</t>
+        </is>
+      </c>
+    </row>
     <row r="250">
-      <c r="A250" s="3" t="inlineStr">
-        <is>
-          <t>Req. ID</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="C250" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D250" s="3" t="inlineStr">
-        <is>
-          <t>중요도/긴급도</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>요청자</t>
-        </is>
-      </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="G250" s="3" t="inlineStr">
-        <is>
-          <t>변경사항</t>
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>- 상세 설계/구현 연결은 Req -&gt; 03/0301/0302/0303/0304 체인으로 확인한다.</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="4" t="inlineStr">
-        <is>
-          <t>Req_027~Req_034</t>
-        </is>
-      </c>
-      <c r="B251" s="4" t="inlineStr">
-        <is>
-          <t>경고 중재 시나리오 요구</t>
-        </is>
-      </c>
-      <c r="C251" s="4" t="inlineStr">
-        <is>
-          <t>긴급 우선, 구급 우선, ETA 우선, 종료 후 복귀, 전환 안정화</t>
-        </is>
-      </c>
-      <c r="D251" s="4" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="E251" s="4" t="inlineStr"/>
-      <c r="F251" s="4" t="inlineStr"/>
-      <c r="G251" s="4" t="inlineStr"/>
-    </row>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>Part 5. 표시/HMI 요구사항 (Req_035, Req_037, Req_040)</t>
-        </is>
-      </c>
-    </row>
-    <row r="255"/>
-    <row r="256">
-      <c r="A256" s="3" t="inlineStr">
-        <is>
-          <t>Req. ID</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="C256" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D256" s="3" t="inlineStr">
-        <is>
-          <t>중요도/긴급도</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="inlineStr">
-        <is>
-          <t>요청자</t>
-        </is>
-      </c>
-      <c r="F256" s="3" t="inlineStr">
-        <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="G256" s="3" t="inlineStr">
-        <is>
-          <t>변경사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="4" t="inlineStr">
-        <is>
-          <t>Req_035, Req_037, Req_040</t>
-        </is>
-      </c>
-      <c r="B257" s="4" t="inlineStr">
-        <is>
-          <t>표시 정책 요구</t>
-        </is>
-      </c>
-      <c r="C257" s="4" t="inlineStr">
-        <is>
-          <t>긴급 시각표현(색+패턴), 구간별 고정 패턴, 경고 문구 기준</t>
-        </is>
-      </c>
-      <c r="D257" s="4" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="E257" s="4" t="inlineStr"/>
-      <c r="F257" s="4" t="inlineStr"/>
-      <c r="G257" s="4" t="inlineStr"/>
-    </row>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>Part 6. 검증/인수 조건 (Verification Environment Requirement, Req_041~Req_043, Req_110~Req_112)</t>
-        </is>
-      </c>
-    </row>
-    <row r="261"/>
-    <row r="262">
-      <c r="A262" s="3" t="inlineStr">
-        <is>
-          <t>Req. ID</t>
-        </is>
-      </c>
-      <c r="B262" s="3" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="C262" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D262" s="3" t="inlineStr">
-        <is>
-          <t>중요도/긴급도</t>
-        </is>
-      </c>
-      <c r="E262" s="3" t="inlineStr">
-        <is>
-          <t>요청자</t>
-        </is>
-      </c>
-      <c r="F262" s="3" t="inlineStr">
-        <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="G262" s="3" t="inlineStr">
-        <is>
-          <t>변경사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="4" t="inlineStr">
-        <is>
-          <t>Req_041~Req_043, Req_110~Req_112</t>
-        </is>
-      </c>
-      <c r="B263" s="4" t="inlineStr">
-        <is>
-          <t>검증/인수 조건 요구</t>
-        </is>
-      </c>
-      <c r="C263" s="4" t="inlineStr">
-        <is>
-          <t>고객 요구 검증을 위한 SIL 수행성, CAN+Ethernet 동시 검증 수행성, 시나리오 판정/기록 수행성과 도메인 게이트웨이 전달/통신 경계 유지 검증 수행성, 차량 기본 기능 SIL 검증 수행성</t>
-        </is>
-      </c>
-      <c r="D263" s="4" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="E263" s="4" t="inlineStr"/>
-      <c r="F263" s="4" t="inlineStr"/>
-      <c r="G263" s="4" t="inlineStr"/>
-    </row>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>Part 7. V2/ADAS 확장 요구사항 (Req_120~Req_121, Req_123, Req_125~Req_129, Req_130~Req_139)</t>
-        </is>
-      </c>
-    </row>
-    <row r="267"/>
-    <row r="268">
-      <c r="A268" s="3" t="inlineStr">
-        <is>
-          <t>Req. ID</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="C268" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D268" s="3" t="inlineStr">
-        <is>
-          <t>중요도/긴급도</t>
-        </is>
-      </c>
-      <c r="E268" s="3" t="inlineStr">
-        <is>
-          <t>요청자</t>
-        </is>
-      </c>
-      <c r="F268" s="3" t="inlineStr">
-        <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="G268" s="3" t="inlineStr">
-        <is>
-          <t>변경사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="4" t="inlineStr">
-        <is>
-          <t>Req_120~Req_121, Req_123, Req_125~Req_129, Req_130~Req_139</t>
-        </is>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>복합중재 + Fail-safe + 객체인지 확장 요구</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="inlineStr">
-        <is>
-          <t>긴급차량 근접 위험 기반 감속 보조 요청, 도메인 단절 강등, 객체 기반 TTC/교차로/합류 위험 경고 정책</t>
-        </is>
-      </c>
-      <c r="D269" s="4" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="E269" s="4" t="inlineStr"/>
-      <c r="F269" s="4" t="inlineStr"/>
-      <c r="G269" s="4" t="inlineStr"/>
-    </row>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>Part 8. Legacy 전환 관리 (통합/분할 대체 Req)</t>
-        </is>
-      </c>
-    </row>
-    <row r="273"/>
-    <row r="274">
-      <c r="A274" s="3" t="inlineStr">
-        <is>
-          <t>Req. ID</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="C274" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D274" s="3" t="inlineStr">
-        <is>
-          <t>중요도/긴급도</t>
-        </is>
-      </c>
-      <c r="E274" s="3" t="inlineStr">
-        <is>
-          <t>요청자</t>
-        </is>
-      </c>
-      <c r="F274" s="3" t="inlineStr">
-        <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="G274" s="3" t="inlineStr">
-        <is>
-          <t>변경사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="4" t="inlineStr">
-        <is>
-          <t>Req_018, Req_036, Req_038, Req_039, Req_108, Req_114, Req_115, Req_117, Req_122, Req_124</t>
-        </is>
-      </c>
-      <c r="B275" s="4" t="inlineStr">
-        <is>
-          <t>Legacy 매핑 요구</t>
-        </is>
-      </c>
-      <c r="C275" s="4" t="inlineStr">
-        <is>
-          <t>통합/분할 개편으로 대체된 기존 Req를 Legacy 참조로 유지하고 신규 Active Req와 매핑 추적</t>
-        </is>
-      </c>
-      <c r="D275" s="4" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="E275" s="4" t="inlineStr"/>
-      <c r="F275" s="4" t="inlineStr"/>
-      <c r="G275" s="4" t="inlineStr">
-        <is>
-          <t>전환 단계 한정 운영</t>
-        </is>
-      </c>
-    </row>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>Part 9. 차량 경보 편의 확장 요구사항 (Pre-Activation, Req_140~Req_147)</t>
-        </is>
-      </c>
-    </row>
-    <row r="279"/>
-    <row r="280">
-      <c r="A280" s="3" t="inlineStr">
-        <is>
-          <t>Req. ID</t>
-        </is>
-      </c>
-      <c r="B280" s="3" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="C280" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D280" s="3" t="inlineStr">
-        <is>
-          <t>중요도/긴급도</t>
-        </is>
-      </c>
-      <c r="E280" s="3" t="inlineStr">
-        <is>
-          <t>요청자</t>
-        </is>
-      </c>
-      <c r="F280" s="3" t="inlineStr">
-        <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="G280" s="3" t="inlineStr">
-        <is>
-          <t>변경사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="4" t="inlineStr">
-        <is>
-          <t>Req_140~Req_147</t>
-        </is>
-      </c>
-      <c r="B281" s="4" t="inlineStr">
-        <is>
-          <t>차량 경보 편의 확장 요구</t>
-        </is>
-      </c>
-      <c r="C281" s="4" t="inlineStr">
-        <is>
-          <t>방향지시등/주행모드/안전벨트 입력을 경보 정책에 연동하고, 접근 거리 표시/이벤트 기록·조회/표시방식·음량 설정 반영을 확장</t>
-        </is>
-      </c>
-      <c r="D281" s="4" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="E281" s="4" t="inlineStr"/>
-      <c r="F281" s="4" t="inlineStr"/>
-      <c r="G281" s="4" t="inlineStr">
-        <is>
-          <t>신규(Pre-Activation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>Part 10. 경고 강건성·인지성 확장 요구사항 (Pre-Activation, Req_148~Req_155)</t>
-        </is>
-      </c>
-    </row>
-    <row r="285"/>
-    <row r="286">
-      <c r="A286" s="3" t="inlineStr">
-        <is>
-          <t>Req. ID</t>
-        </is>
-      </c>
-      <c r="B286" s="3" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="C286" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D286" s="3" t="inlineStr">
-        <is>
-          <t>중요도/긴급도</t>
-        </is>
-      </c>
-      <c r="E286" s="3" t="inlineStr">
-        <is>
-          <t>요청자</t>
-        </is>
-      </c>
-      <c r="F286" s="3" t="inlineStr">
-        <is>
-          <t>검토자</t>
-        </is>
-      </c>
-      <c r="G286" s="3" t="inlineStr">
-        <is>
-          <t>변경사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="4" t="inlineStr">
-        <is>
-          <t>Req_148~Req_155</t>
-        </is>
-      </c>
-      <c r="B287" s="4" t="inlineStr">
-        <is>
-          <t>경고 강건성·인지성 확장 요구</t>
-        </is>
-      </c>
-      <c r="C287" s="4" t="inlineStr">
-        <is>
-          <t>입력 유효성/신선도 보호, 상태 전이 안정화, 출력 채널 가용성·대체 출력 유지, 오디오 경합/팝업 과밀 제어, 채널 동기 일관성 관리</t>
-        </is>
-      </c>
-      <c r="D287" s="4" t="inlineStr">
-        <is>
-          <t>혼합</t>
-        </is>
-      </c>
-      <c r="E287" s="4" t="inlineStr"/>
-      <c r="F287" s="4" t="inlineStr"/>
-      <c r="G287" s="4" t="inlineStr">
-        <is>
-          <t>신규(Pre-Activation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291">
-      <c r="A291" s="2" t="inlineStr">
-        <is>
-          <t>요구사항 사용 가이드</t>
-        </is>
-      </c>
-    </row>
-    <row r="292"/>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>- 대외 설명/발표 기준 문서: 상단 통합 기본요구사항(Req_001~Req_040)</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>- 차량 기본 기능 확장 기준: 상단 차량 기본 기능 요구사항(Req_101~Req_107, Req_109, Req_113, Req_116, Req_118~Req_119)</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>- 검증/인수 조건 기준: 하단 Part 6. 검증/인수 조건(Req_041~Req_043, Req_110~Req_112)</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>- V2 확장 기준: 하단 Part 7. V2/ADAS 확장 요구사항(Req_120~Req_121, Req_123, Req_125~Req_129, Req_130~Req_139)</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>- Legacy 전환 기준: 하단 Part 8. Legacy 전환 관리(Req_018/036/038/039/108/114/115/117/122/124)</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>- 차량 경보 편의 확장 기준: 하단 Part 9. 차량 경보 편의 확장 요구사항(Req_140~Req_147)</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>- 경고 강건성·인지성 확장 기준: 하단 Part 10. 경고 강건성·인지성 확장 요구사항(Req_148~Req_155)</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>- 내부 작업 분배 기준: 하단 Part별 요구사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>- 상세 설계 연결 시: 각 Req ID를 03/0301/0302/0303/0304 및 05/06/07에 누락 없는 N:M 커버리지로 매핑</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>- 전환 단계 원칙: 체인 동기화 완료 전까지 Legacy Req는 삭제하지 않고 신규 Req와 매핑표로 추적한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>- 팀 운영 규칙 1: 물리 하드웨어 없이 CANoe 가상환경에서 검증한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>- 팀 운영 규칙 2: 검증 네트워크 범위는 CAN + Ethernet으로 고정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>- 팀 운영 규칙 3: 주요 시나리오별 합격/불합격 기준을 사전에 정의한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>- 팀 운영 규칙 4: 요구사항별 검증 결과를 추적 가능한 형태로 기록한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>- 팀 운영 규칙 5: 임의 Req를 점검해도 문서 추적이 끊기지 않게 유지한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>- 팀 운영 규칙 6: 프로젝트 종료 시 충족 여부를 단일 요약 문서로 확인 가능하게 정리한다.</t>
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>- 시험 연결은 VC -&gt; 05/06/07 기준으로 추적한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>- Legacy/Pre-Activation 상태 표기는 원문 SoT와 동일하게 유지한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>- 검증/인수 조건(Part 6)은 고객 기능 요구와 분리하여 관리한다.</t>
         </is>
       </c>
     </row>
@@ -15469,15 +14867,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16847,6 +16246,275 @@
       <c r="D97" s="4" t="inlineStr">
         <is>
           <t>경고 입력 유효성/신뢰도 보호(Pre-Activation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>대표 체인 샘플 (제출 보강)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Req ID</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Func ID</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Flow ID</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Comm ID</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Var ID(핵심)</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>Code Ref</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Test Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Req_001</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Func_001</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Flow_001</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Comm_001</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Var_012(vehicleSpeedNorm), Var_013(driveStateNorm)</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>MOD_01.F001</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>UT_ADAS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Req_017</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Func_017</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Flow_004</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Comm_004</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Var_007(emergencyType), Var_009(eta)</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>MOD_03.F017</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>UT_EMS_POL_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Req_022</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Func_022</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Flow_006</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Comm_006</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Var_017(emergencyContext), Var_018(selectedAlertLevel)</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>MOD_06.F022</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>UT_ARB_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Req_035</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Func_035</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Flow_007</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Comm_007</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Var_019(selectedAlertType), Var_022(ambientColor)</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>MOD_11.F035</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>UT_BCM_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Req_120</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Func_120</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Flow_120</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Comm_120</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Var_320(proximityRiskLevel)</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>MOD_01.F120</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>UT_V2_RISK_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Req_130</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Func_130</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Flow_130</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Comm_130</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Var_330(objectTrackValid), Var_331(objectRange)</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>MOD_01.F130</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>UT_ADAS_OBJ_RISK_001 (Planned)</t>
         </is>
       </c>
     </row>
@@ -16861,11 +16529,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG182"/>
+  <dimension ref="A1:AG169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="75" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
@@ -16931,14 +16599,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Version: 3.23</t>
+          <t>Version: 3.24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Date: 2026-03-06</t>
+          <t>Date: 2026-03-07</t>
         </is>
       </c>
     </row>
@@ -24877,452 +24545,658 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Flow 원본(Source of Truth) 매핑</t>
+          <t>Flow SoT 요약 (제출본)</t>
         </is>
       </c>
     </row>
     <row r="133"/>
     <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>계층</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>적용 Flow ID</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>원본 파일(SoT)</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>유지 규칙</t>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>- CAN Flow 원본: canoe/databases/*.dbc</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>Core CAN Profile</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>Flow_001, Flow_002, Flow_003(CAN), Flow_007(CAN 0x289), Flow_008(CAN 0x280), Flow_009(CAN 0x2A5)</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/databases/chassis_can.dbc` + `canoe/databases/infotainment_can.dbc` + `canoe/databases/body_can.dbc` + `canoe/databases/adas_can.dbc` + `canoe/databases/eth_backbone_can_stub.dbc`</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>상단 공식표와 동일 ID/Signal 유지(CAN-stub 포함)</t>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>- Ethernet 논리 계약 원본: canoe/docs/operations/ETH_INTERFACE_CONTRACT.md (v1.2)</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>Core Ethernet Profile</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>Flow_001~Flow_008(Ethernet 구간)</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/docs/operations/ETH_INTERFACE_CONTRACT.md`</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>E100/E200, 0x510/0x511/0x512 계약 우선</t>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>- ADAS 객체 확장(Flow_130~133)은 계약 SoT 활성 + 구현/시험 Pre-Activation 상태로 유지한다.</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>Chassis Domain Profile</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>Flow_102, Flow_106(일부), Flow_105(헬스 연계), Flow_201</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/databases/chassis_can.dbc`</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr">
-        <is>
-          <t>0x122~0x2A0(0x1C1 제외) 범위 준수</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>ADAS Domain CAN Profile</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>Flow_120, Flow_201(일부)</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/databases/adas_can.dbc`</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr">
-        <is>
-          <t>0x1C1/0x1C3 범위 준수 (ADAS 소유 프레임)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>ETH Backbone CAN Stub Profile</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>Flow_004, Flow_005, Flow_006, Flow_121, Flow_124</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/databases/eth_backbone_can_stub.dbc`</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>0x1C0/0x1C2/0x1C4/0x111 범위 준수</t>
-        </is>
-      </c>
-    </row>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>- Flow 변경 시 0303/0304/04/05/06/07 동시 동기화를 적용한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138"/>
+    <row r="139"/>
     <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>ADAS Object Extension Profile (Pending)</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>Flow_130~Flow_133</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/docs/operations/ETH_INTERFACE_CONTRACT.md` (v1.2 예정)</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>Pre-Activation, `E213~E216` 계약 반영 전에는 활성 SoT로 사용하지 않음</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>Powertrain Domain Profile</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>Flow_101, Flow_105, Flow_204</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/databases/powertrain_can.dbc`</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>0x110~0x2A8 범위 준수</t>
-        </is>
-      </c>
-    </row>
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>플로우 상세 추적 표 (Flow/Func/Req)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141"/>
     <row r="142">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>Body Domain Profile</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>Flow_103, Flow_105, Flow_202</t>
-        </is>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/databases/body_can.dbc`</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr">
-        <is>
-          <t>0x289~0x291, 0x277~0x292 범위 준수</t>
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Flow ID</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Comm ID(0303 연계)</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Func ID</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Req ID</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>관련 메시지(ID)</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>Tx Node</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>Rx Node</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>Active Condition</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>Clear Condition</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Infotainment Domain Profile</t>
+          <t>Flow_001</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Flow_104, Flow_105, Flow_203, Flow_205</t>
+          <t>Comm_001</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>`canoe/databases/infotainment_can.dbc`</t>
+          <t>Func_001, Func_002, Func_003, Func_004, Func_006, Func_010</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>0x2A3, 0x280~0x288, 0x289~0x295 범위 준수</t>
-        </is>
-      </c>
-    </row>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
+          <t>Req_001, Req_002, Req_003, Req_004, Req_006, Req_010</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>frmVehicleStateCanMsg(0x2A0), ethVehicleStateMsg(0x510)</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>VAL_SCENARIO_CTRL, CHS_GW</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>CHS_GW, ADAS_WARN_CTRL</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>CAN + Ethernet(UDP)</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>속도/주행상태 입력 갱신</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>경고 조건 해제 또는 입력 무효</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>Flow_002</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>Comm_002</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Func_011, Func_012</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Req_011, Req_012</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>frmSteeringCanMsg(0x2A1), ethSteeringMsg(0x511)</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>VAL_SCENARIO_CTRL, CHS_GW</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>CHS_GW, ADAS_WARN_CTRL</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>CAN + Ethernet(UDP)</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>조향 입력 갱신</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>조향 입력 검출 또는 경고 해제</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>Flow_003</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Comm_003</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Func_007, Func_010</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Req_007, Req_010</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>frmNavContextCanMsg(0x2A3), ethNavContextMsg(0x512)</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>VAL_SCENARIO_CTRL, INFOTAINMENT_GW</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>INFOTAINMENT_GW, NAV_CTX_MGR, ADAS_WARN_CTRL, WARN_ARB_MGR</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>CAN + Ethernet(UDP)</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>구간/방향/거리/제한속도 입력 갱신</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>다음 컨텍스트 수신 시 갱신</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>Flow_004</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>Comm_004</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Func_017</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Req_017</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>ETH_EmergencyAlert(0xE100)</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>EMS_ALERT(Tx:Police)</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>EMS_ALERT(Rx)</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>Ethernet(UDP)</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>Police_Active=1</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>alertState=Clear 또는 송신 중지</t>
+        </is>
+      </c>
+    </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>플로우 상세 추적 표 (Flow/Func/Req)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148"/>
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Flow_005</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Comm_005</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>Func_018</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Req_017</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>ETH_EmergencyAlert(0xE100)</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>EMS_ALERT(Tx:Ambulance)</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>EMS_ALERT(Rx)</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>Ethernet(UDP)</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>Ambulance_Active=1</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>alertState=Clear 또는 송신 중지</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>Flow_006</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Comm_006</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Func_022, Func_023, Func_024, Func_025, Func_027, Func_028, Func_029, Func_030, Func_031, Func_032, Func_144, Func_149, Func_150, Func_152</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>Req_022, Req_023, Req_024, Req_025, Req_027, Req_028, Req_029, Req_030, Req_031, Req_032, Req_144, Req_149, Req_150, Req_152</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>ETH_EmergencyAlert(0xE100), ethSelectedAlertMsg(0xE200)</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>EMS_ALERT(Rx), WARN_ARB_MGR</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>WARN_ARB_MGR, BODY_GW, IVI_GW</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>Ethernet(UDP)</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>Event + 50ms</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>EmergencyAlert 수신 또는 Zone 충돌 발생</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>Clear 수신 또는 1000ms 무갱신</t>
+        </is>
+      </c>
+    </row>
     <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>Flow ID</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>Comm ID(0303 연계)</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>Func ID</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>Req ID</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>관련 메시지(ID)</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>Tx Node</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>Rx Node</t>
-        </is>
-      </c>
-      <c r="H149" s="3" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="I149" s="3" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>Active Condition</t>
-        </is>
-      </c>
-      <c r="K149" s="3" t="inlineStr">
-        <is>
-          <t>Clear Condition</t>
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Flow_007</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Comm_007</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Func_008, Func_009, Func_013, Func_014, Func_015, Func_016, Func_033, Func_034, Func_035, Func_036, Func_037, Func_038, Func_039, Func_152</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Req_008, Req_009, Req_013, Req_014, Req_015, Req_016, Req_033, Req_034, Req_035, Req_037, Req_152</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>ethSelectedAlertMsg(0xE200), frmAmbientControlMsg(0x260)</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>WARN_ARB_MGR, BODY_GW</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>BODY_GW, AMBIENT_CTRL</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>Ethernet(UDP) + CAN</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>50ms</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>selectedAlertLevel/selectedAlertType 수신</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>timeoutClear=1 또는 기본 상태 복귀</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>Flow_001</t>
+          <t>Flow_008</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Comm_001</t>
+          <t>Comm_008</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Func_001, Func_002, Func_003, Func_004, Func_006, Func_010</t>
+          <t>Func_005, Func_019, Func_020, Func_021, Func_026, Func_040, Func_143, Func_152, Func_155</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Req_001, Req_002, Req_003, Req_004, Req_006, Req_010</t>
+          <t>Req_005, Req_019, Req_020, Req_021, Req_026, Req_040, Req_143, Req_152, Req_155</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>frmVehicleStateCanMsg(0x2A0), ethVehicleStateMsg(0x510)</t>
+          <t>ethSelectedAlertMsg(0xE200), frmClusterWarningMsg(0x280)</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>VAL_SCENARIO_CTRL, CHS_GW</t>
+          <t>WARN_ARB_MGR, IVI_GW</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>CHS_GW, ADAS_WARN_CTRL</t>
+          <t>IVI_GW, CLU_HMI_CTRL</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>CAN + Ethernet(UDP)</t>
+          <t>Ethernet(UDP) + CAN</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>50ms</t>
         </is>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>속도/주행상태 입력 갱신</t>
+          <t>selectedAlertLevel/selectedAlertType 수신</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>경고 조건 해제 또는 입력 무효</t>
+          <t>alertState 해제 또는 문구 만료</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Flow_002</t>
+          <t>Flow_009</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Comm_002</t>
+          <t>Comm_009</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Func_011, Func_012</t>
+          <t>Func_041, Func_042, Func_043</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Req_011, Req_012</t>
+          <t>Req_041, Req_042, Req_043</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>frmSteeringCanMsg(0x2A1), ethSteeringMsg(0x511)</t>
+          <t>frmTestResultMsg(0x2A5)</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>VAL_SCENARIO_CTRL, CHS_GW</t>
+          <t>VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>CHS_GW, ADAS_WARN_CTRL</t>
+          <t>VAL_SCENARIO_CTRL(Log/Panel)</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>CAN + Ethernet(UDP)</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>조향 입력 갱신</t>
+          <t>시나리오 실행 시작</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>조향 입력 검출 또는 경고 해제</t>
+          <t>판정 결과 기록 완료 (Validation-only)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>Flow_003</t>
+          <t>Flow_120</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Comm_003</t>
+          <t>Comm_120</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Func_007, Func_010</t>
+          <t>Func_120</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Req_007, Req_010</t>
+          <t>Req_120</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>frmNavContextCanMsg(0x2A3), ethNavContextMsg(0x512)</t>
+          <t>ethEmergencyRiskMsg(0x1C3)</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>VAL_SCENARIO_CTRL, INFOTAINMENT_GW</t>
+          <t>ADAS_WARN_CTRL</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>INFOTAINMENT_GW, NAV_CTX_MGR, ADAS_WARN_CTRL, WARN_ARB_MGR</t>
+          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>CAN + Ethernet(UDP)</t>
+          <t>Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
@@ -25332,1002 +25206,507 @@
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>구간/방향/거리/제한속도 입력 갱신</t>
+          <t>emergencyDirection/ETA/vehicleSpeed 갱신</t>
         </is>
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>다음 컨텍스트 수신 시 갱신</t>
+          <t>위험도 입력 무효 또는 긴급 해제</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Flow_004</t>
+          <t>Flow_121</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Comm_004</t>
+          <t>Comm_121</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Func_017</t>
+          <t>Func_121</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Req_017</t>
+          <t>Req_121</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>ETH_EmergencyAlert(0xE100)</t>
+          <t>ethDecelAssistReqMsg(0x1C4)</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT(Tx:Police)</t>
+          <t>WARN_ARB_MGR</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT(Rx)</t>
+          <t>CHS_GW, BRK_CTRL, VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP)</t>
+          <t>Ethernet(UDP) + CAN</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>Event + 50ms</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>Police_Active=1</t>
+          <t>proximityRiskLevel 임계 초과</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>alertState=Clear 또는 송신 중지</t>
+          <t>임계 미만 또는 failSafeMode=1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Flow_005</t>
+          <t>Flow_122</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Comm_005</t>
+          <t>Comm_122</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Func_018</t>
+          <t>Func_125,Func_126</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Req_017</t>
+          <t>Req_125,Req_126</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>ETH_EmergencyAlert(0xE100)</t>
+          <t>ethSelectedAlertMsg(0xE200), frmAmbientControlMsg(0x260), frmClusterWarningMsg(0x280)</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT(Tx:Ambulance)</t>
+          <t>WARN_ARB_MGR</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT(Rx)</t>
+          <t>BODY_GW, IVI_GW, AMBIENT_CTRL, CLU_HMI_CTRL</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP)</t>
+          <t>Ethernet(UDP) + CAN</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>50ms</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>Ambulance_Active=1</t>
+          <t>decelAssistReq=1</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>alertState=Clear 또는 송신 중지</t>
+          <t>decelAssistReq=0 또는 긴급 해제</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Flow_006</t>
+          <t>Flow_123</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Comm_006</t>
+          <t>Comm_123</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Func_022, Func_023, Func_024, Func_025, Func_027, Func_028, Func_029, Func_030, Func_031, Func_032, Func_144, Func_149, Func_150, Func_152</t>
+          <t>Func_123</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Req_022, Req_023, Req_024, Req_025, Req_027, Req_028, Req_029, Req_030, Req_031, Req_032, Req_144, Req_149, Req_150, Req_152</t>
+          <t>Req_123</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>ETH_EmergencyAlert(0xE100), ethSelectedAlertMsg(0xE200)</t>
+          <t>frmPedalInputCanMsg(0x2A2), frmSteeringCanMsg(0x2A1), ethDecelAssistReqMsg(0x1C4)</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT(Rx), WARN_ARB_MGR</t>
+          <t>CHS_GW, WARN_ARB_MGR</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR, BODY_GW, IVI_GW</t>
+          <t>WARN_ARB_MGR, DOMAIN_ROUTER, BRK_CTRL</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP)</t>
+          <t>CAN + Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>Event + 50ms</t>
+          <t>Event + 100ms</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>EmergencyAlert 수신 또는 Zone 충돌 발생</t>
+          <t>운전자 제동/조향 회피 입력 검출</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>Clear 수신 또는 1000ms 무갱신</t>
+          <t>decelAssistReq=0 전환 완료</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Flow_007</t>
+          <t>Flow_124</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Comm_007</t>
+          <t>Comm_124</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Func_008, Func_009, Func_013, Func_014, Func_015, Func_016, Func_033, Func_034, Func_035, Func_036, Func_037, Func_038, Func_039, Func_152</t>
+          <t>Func_127,Func_128,Func_129,Func_151,Func_152</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Req_008, Req_009, Req_013, Req_014, Req_015, Req_016, Req_033, Req_034, Req_035, Req_037, Req_152</t>
+          <t>Req_127,Req_128,Req_129,Req_151,Req_152</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>ethSelectedAlertMsg(0xE200), frmAmbientControlMsg(0x260)</t>
+          <t>frmChassisHealthMsg(0x103), frmBodyHealthMsg(0x269), frmInfotainmentHealthMsg(0x288), ethFailSafeStateMsg(0x111)</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR, BODY_GW</t>
+          <t>CHS_GW, BODY_GW, INFOTAINMENT_GW, DOMAIN_BOUNDARY_MGR</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>BODY_GW, AMBIENT_CTRL</t>
+          <t>DOMAIN_BOUNDARY_MGR, DOMAIN_ROUTER, WARN_ARB_MGR, BODY_GW, IVI_GW, VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP) + CAN</t>
+          <t>CAN + Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>50ms</t>
+          <t>100ms + Event</t>
         </is>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>selectedAlertLevel/selectedAlertType 수신</t>
+          <t>domainPathStatus=FAILED 또는 forceFailSafe=1</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>timeoutClear=1 또는 기본 상태 복귀</t>
+          <t>경로 복구 + Health 정상화</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>Flow_008</t>
+          <t>Flow_130</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Comm_008</t>
+          <t>Comm_130</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Func_005, Func_019, Func_020, Func_021, Func_026, Func_040, Func_143, Func_152, Func_155</t>
+          <t>Func_130,Func_131,Func_148</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Req_005, Req_019, Req_020, Req_021, Req_026, Req_040, Req_143, Req_152, Req_155</t>
+          <t>Req_130,Req_131,Req_148</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>ethSelectedAlertMsg(0xE200), frmClusterWarningMsg(0x280)</t>
+          <t>ethObjectRiskInputMsg(0xE213)</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR, IVI_GW</t>
+          <t>CHS_GW, INFOTAINMENT_GW</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>IVI_GW, CLU_HMI_CTRL</t>
+          <t>ADAS_WARN_CTRL</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP) + CAN</t>
+          <t>Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>50ms</t>
+          <t>100ms</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>selectedAlertLevel/selectedAlertType 수신</t>
+          <t>객체 목록/자차 상태 갱신</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>alertState 해제 또는 문구 만료</t>
+          <t>객체 입력 무효 또는 유효 객체 0건</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>Flow_009</t>
+          <t>Flow_131</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Comm_009</t>
+          <t>Comm_131</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Func_041, Func_042, Func_043</t>
+          <t>Func_132,Func_133,Func_136</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Req_041, Req_042, Req_043</t>
+          <t>Req_132,Req_133,Req_136</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>frmTestResultMsg(0x2A5)</t>
+          <t>ethObjectRiskStateMsg(0xE214)</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>VAL_SCENARIO_CTRL</t>
+          <t>ADAS_WARN_CTRL</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>VAL_SCENARIO_CTRL(Log/Panel)</t>
+          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>100ms + Event</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>시나리오 실행 시작</t>
+          <t>TTC/상대속도/거리 기반 위험도 갱신</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>판정 결과 기록 완료 (Validation-only)</t>
+          <t>TTC 임계 해제 + 유지시간 만료</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>Flow_120</t>
+          <t>Flow_132</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Comm_120</t>
+          <t>Comm_132</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Func_120</t>
+          <t>Func_134,Func_135,Func_139</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Req_120</t>
+          <t>Req_134,Req_135,Req_139</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>ethEmergencyRiskMsg(0x1C3)</t>
+          <t>ethObjectScenarioAlertMsg(0xE215), frmAmbientControlMsg(0x260), frmClusterWarningMsg(0x280)</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>ADAS_WARN_CTRL</t>
+          <t>WARN_ARB_MGR</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
+          <t>BODY_GW, IVI_GW, AMBIENT_CTRL, CLU_HMI_CTRL</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP)</t>
+          <t>Ethernet(UDP) + CAN</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>Event + 50ms</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>emergencyDirection/ETA/vehicleSpeed 갱신</t>
+          <t>교차로/합류 위험 조건 성립</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>위험도 입력 무효 또는 긴급 해제</t>
+          <t>조건 해제 또는 긴급 우선 경고 전환</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>Flow_121</t>
+          <t>Flow_133</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Comm_121</t>
+          <t>Comm_133</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Func_121</t>
+          <t>Func_137,Func_138,Func_148</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Req_121</t>
+          <t>Req_137,Req_138,Req_148</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>ethDecelAssistReqMsg(0x1C4)</t>
+          <t>ethObjectSafetyStateMsg(0xE216)</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR</t>
+          <t>DOMAIN_BOUNDARY_MGR, EMS_ALERT</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>CHS_GW, BRK_CTRL, VAL_SCENARIO_CTRL</t>
+          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP) + CAN</t>
+          <t>Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>Event + 50ms</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>proximityRiskLevel 임계 초과</t>
+          <t>객체 신뢰도 저하 또는 이벤트 발생</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>임계 미만 또는 failSafeMode=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>Flow_122</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>Comm_122</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>Func_125,Func_126</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr">
-        <is>
-          <t>Req_125,Req_126</t>
-        </is>
-      </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>ethSelectedAlertMsg(0xE200), frmAmbientControlMsg(0x260), frmClusterWarningMsg(0x280)</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr">
-        <is>
-          <t>WARN_ARB_MGR</t>
-        </is>
-      </c>
-      <c r="G161" s="4" t="inlineStr">
-        <is>
-          <t>BODY_GW, IVI_GW, AMBIENT_CTRL, CLU_HMI_CTRL</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>Ethernet(UDP) + CAN</t>
-        </is>
-      </c>
-      <c r="I161" s="4" t="inlineStr">
-        <is>
-          <t>50ms</t>
-        </is>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>decelAssistReq=1</t>
-        </is>
-      </c>
-      <c r="K161" s="4" t="inlineStr">
-        <is>
-          <t>decelAssistReq=0 또는 긴급 해제</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>Flow_123</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>Comm_123</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>Func_123</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr">
-        <is>
-          <t>Req_123</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="inlineStr">
-        <is>
-          <t>frmPedalInputCanMsg(0x2A2), frmSteeringCanMsg(0x2A1), ethDecelAssistReqMsg(0x1C4)</t>
-        </is>
-      </c>
-      <c r="F162" s="4" t="inlineStr">
-        <is>
-          <t>CHS_GW, WARN_ARB_MGR</t>
-        </is>
-      </c>
-      <c r="G162" s="4" t="inlineStr">
-        <is>
-          <t>WARN_ARB_MGR, DOMAIN_ROUTER, BRK_CTRL</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>CAN + Ethernet(UDP)</t>
-        </is>
-      </c>
-      <c r="I162" s="4" t="inlineStr">
-        <is>
-          <t>Event + 100ms</t>
-        </is>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>운전자 제동/조향 회피 입력 검출</t>
-        </is>
-      </c>
-      <c r="K162" s="4" t="inlineStr">
-        <is>
-          <t>decelAssistReq=0 전환 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t>Flow_124</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>Comm_124</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>Func_127,Func_128,Func_129,Func_151,Func_152</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr">
-        <is>
-          <t>Req_127,Req_128,Req_129,Req_151,Req_152</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>frmChassisHealthMsg(0x103), frmBodyHealthMsg(0x269), frmInfotainmentHealthMsg(0x288), ethFailSafeStateMsg(0x111)</t>
-        </is>
-      </c>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>CHS_GW, BODY_GW, INFOTAINMENT_GW, DOMAIN_BOUNDARY_MGR</t>
-        </is>
-      </c>
-      <c r="G163" s="4" t="inlineStr">
-        <is>
-          <t>DOMAIN_BOUNDARY_MGR, DOMAIN_ROUTER, WARN_ARB_MGR, BODY_GW, IVI_GW, VAL_SCENARIO_CTRL</t>
-        </is>
-      </c>
-      <c r="H163" s="4" t="inlineStr">
-        <is>
-          <t>CAN + Ethernet(UDP)</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="inlineStr">
-        <is>
-          <t>100ms + Event</t>
-        </is>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>domainPathStatus=FAILED 또는 forceFailSafe=1</t>
-        </is>
-      </c>
-      <c r="K163" s="4" t="inlineStr">
-        <is>
-          <t>경로 복구 + Health 정상화</t>
-        </is>
-      </c>
-    </row>
+          <t>신뢰도 회복 + 이벤트 기록 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
     <row r="164">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>Flow_130</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>Comm_130</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>Func_130,Func_131,Func_148</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>Req_130,Req_131,Req_148</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>ethObjectRiskInputMsg(0xE213)</t>
-        </is>
-      </c>
-      <c r="F164" s="4" t="inlineStr">
-        <is>
-          <t>CHS_GW, INFOTAINMENT_GW</t>
-        </is>
-      </c>
-      <c r="G164" s="4" t="inlineStr">
-        <is>
-          <t>ADAS_WARN_CTRL</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>Ethernet(UDP)</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="inlineStr">
-        <is>
-          <t>100ms</t>
-        </is>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>객체 목록/자차 상태 갱신</t>
-        </is>
-      </c>
-      <c r="K164" s="4" t="inlineStr">
-        <is>
-          <t>객체 입력 무효 또는 유효 객체 0건</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="4" t="inlineStr">
-        <is>
-          <t>Flow_131</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>Comm_131</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>Func_132,Func_133,Func_136</t>
-        </is>
-      </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>Req_132,Req_133,Req_136</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>ethObjectRiskStateMsg(0xE214)</t>
-        </is>
-      </c>
-      <c r="F165" s="4" t="inlineStr">
-        <is>
-          <t>ADAS_WARN_CTRL</t>
-        </is>
-      </c>
-      <c r="G165" s="4" t="inlineStr">
-        <is>
-          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
-        </is>
-      </c>
-      <c r="H165" s="4" t="inlineStr">
-        <is>
-          <t>Ethernet(UDP)</t>
-        </is>
-      </c>
-      <c r="I165" s="4" t="inlineStr">
-        <is>
-          <t>100ms + Event</t>
-        </is>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>TTC/상대속도/거리 기반 위험도 갱신</t>
-        </is>
-      </c>
-      <c r="K165" s="4" t="inlineStr">
-        <is>
-          <t>TTC 임계 해제 + 유지시간 만료</t>
-        </is>
-      </c>
-    </row>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>제출본 운용 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="165"/>
     <row r="166">
-      <c r="A166" s="4" t="inlineStr">
-        <is>
-          <t>Flow_132</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>Comm_132</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>Func_134,Func_135,Func_139</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>Req_134,Req_135,Req_139</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>ethObjectScenarioAlertMsg(0xE215), frmAmbientControlMsg(0x260), frmClusterWarningMsg(0x280)</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>WARN_ARB_MGR</t>
-        </is>
-      </c>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>BODY_GW, IVI_GW, AMBIENT_CTRL, CLU_HMI_CTRL</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>Ethernet(UDP) + CAN</t>
-        </is>
-      </c>
-      <c r="I166" s="4" t="inlineStr">
-        <is>
-          <t>Event + 50ms</t>
-        </is>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>교차로/합류 위험 조건 성립</t>
-        </is>
-      </c>
-      <c r="K166" s="4" t="inlineStr">
-        <is>
-          <t>조건 해제 또는 긴급 우선 경고 전환</t>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>- 상단 공식 플로우 표와 플로우 상세 추적 표를 제출 기준 본표로 유지한다.</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>Flow_133</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>Comm_133</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>Func_137,Func_138,Func_148</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>Req_137,Req_138,Req_148</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>ethObjectSafetyStateMsg(0xE216)</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>DOMAIN_BOUNDARY_MGR, EMS_ALERT</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>Ethernet(UDP)</t>
-        </is>
-      </c>
-      <c r="I167" s="4" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>객체 신뢰도 저하 또는 이벤트 발생</t>
-        </is>
-      </c>
-      <c r="K167" s="4" t="inlineStr">
-        <is>
-          <t>신뢰도 회복 + 이벤트 기록 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>하단 확장표 축소 (제출본)</t>
-        </is>
-      </c>
-    </row>
-    <row r="172"/>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>- 상단 공식 플로우 표와 플로우 상세 추적 표를 제출 기준 본표로 유지한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>- 도메인별/단계별 확장 분해표는 중복을 줄이기 위해 요약만 남긴다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>- 상세 전수 매핑은 원문 SoT(driving-situation-alert/0302_NWflowDef.md)를 기준으로 관리한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176"/>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>제출본 유지 내용</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>원문 SoT 참조</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>도메인 네트워크 분리</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>Core/Domain 분리 원칙 + 주요 경로 요약</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>0302 원문 `도메인 네트워크 분리 기준`</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>Vehicle Baseline 확장</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>Flow_101~106, Flow_201~205는 `Defined` 상태로 유지</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>0302 원문 Baseline/Phase-B 확장 표</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>V2 확장</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>Flow_120~124는 `Implemented` 상태로 유지</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>0302 원문 V2 확장 표</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>ADAS 객체 인지 확장</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>Flow_130~133는 `Planned(Pre-Activation)` 상태로 유지</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>0302 원문 ADAS 확장 표</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t>동기화 규칙</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>변경 시 0303/0304/04/05/06/07 동시 반영</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>TMP_HANDOFF + 원문 체인</t>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>- Baseline(Flow_101~106, 201~205)은 Defined, V2(Flow_120~124)는 Implemented 상태로 관리한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>- ADAS 객체 확장(Flow_130~133)은 Planned(Pre-Activation) 상태로 유지한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>- 상세 전수 매핑과 도메인 분해표는 원문 SoT(driving-situation-alert/0302_NWflowDef.md)를 기준으로 관리한다.</t>
         </is>
       </c>
     </row>
@@ -26342,7 +25721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J195"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -26354,7 +25733,7 @@
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="71" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="57" customWidth="1" min="10" max="10"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26389,14 +25768,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Version: 3.26</t>
+          <t>Version: 3.27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Date: 2026-03-06</t>
+          <t>Date: 2026-03-07</t>
         </is>
       </c>
     </row>
@@ -26533,7 +25912,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>- ID 상위 SoT는 00f_CAN_ID_Allocation_Standard.md를 따른다.</t>
+          <t>- ID 상위 SoT는 governance/00f_CAN_ID_Allocation_Standard.md를 따른다.</t>
         </is>
       </c>
     </row>
@@ -26577,7 +25956,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Ethernet 논리 ID(`0xE100/0xE200/0xE210~0xE212`)와 CANoe SIL Stub ID(`0x1C3/0x1C4/0x111`)를 분리 표기한다.</t>
+          <t>Ethernet 논리 ID(`0xE100/0xE200/0xE210~0xE216`)와 CANoe SIL Stub ID(`0x1C3/0x1C4/0x111/0x1C5~0x1C8`)를 분리 표기한다.</t>
         </is>
       </c>
     </row>
@@ -30857,267 +30236,348 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>통신 원본(Source of Truth) 매핑</t>
+          <t>Comm SoT 요약 (제출본)</t>
         </is>
       </c>
     </row>
     <row r="149"/>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>범위</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>원본 파일</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>- CAN Comm 원본: canoe/databases/*.dbc</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>Core CAN Profile</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>Comm_001, Comm_002, Comm_003, Comm_007, Comm_008, Comm_009</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/databases/chassis_can.dbc` + `canoe/databases/infotainment_can.dbc` + `canoe/databases/body_can.dbc` + `canoe/databases/adas_can.dbc` + `canoe/databases/eth_backbone_can_stub.dbc`</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>경고 코어 체인 단일 원본(CAN-stub 포함)</t>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>- Ethernet 논리 계약 원본: canoe/docs/operations/ETH_INTERFACE_CONTRACT.md (v1.2)</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="4" t="inlineStr">
-        <is>
-          <t>Domain CAN Profile</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>Comm_101~Comm_106, Comm_201~Comm_205</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/databases/chassis_can.dbc` + `canoe/databases/powertrain_can.dbc` + `canoe/databases/body_can.dbc` + `canoe/databases/infotainment_can.dbc` + `canoe/databases/adas_can.dbc` + `canoe/databases/eth_backbone_can_stub.dbc`</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr">
-        <is>
-          <t>차량 기본 기능/도메인 분리 원본(CAN-stub 포함)</t>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>- ADAS 객체 확장(Comm_130~133)은 계약 SoT 활성 + 구현/시험 Pre-Activation 상태로 유지한다.</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>ADAS CAN Profile</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>Comm_120, Comm_201(일부)</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/databases/adas_can.dbc`</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>ADAS 소유 프레임 원본</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>ETH Stub Transport Profile</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>Comm_004, Comm_005, Comm_006, Comm_121, Comm_124</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/databases/eth_backbone_can_stub.dbc`</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>CANoe.CAN 환경 대체 운반 원본</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>Ethernet Profile (Logical Contract)</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>Comm_004, Comm_005, Comm_006, Comm_120, Comm_121, Comm_124 (및 Comm_001~003/007~008의 ETH 구간)</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/docs/operations/ETH_INTERFACE_CONTRACT.md`</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>UDP 활성 계약 단일 원본</t>
-        </is>
-      </c>
-    </row>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>- Comm 변경 시 0302/0304/04/05/06/07 동시 동기화를 적용한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154"/>
+    <row r="155"/>
     <row r="156">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>Ethernet Profile (Pending-PreActivation)</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>Comm_130~Comm_133</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>`canoe/docs/operations/ETH_INTERFACE_CONTRACT.md` (v1.2 예정)</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>`E213~E216` 계약 반영 전에는 참조 전용(활성 SoT 아님)</t>
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>통신 상세 추적 표 (Comm/Flow/Func/Req)</t>
         </is>
       </c>
     </row>
     <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>Comm ID</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Flow ID</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Func ID</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Req ID</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>Message(ID)</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>Tx Node</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>Rx Node</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>Clear/비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>Comm_001</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>Flow_001</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>Func_001, Func_002, Func_003, Func_004, Func_006, Func_010</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Req_001, Req_002, Req_003, Req_004, Req_006, Req_010</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>frmVehicleStateCanMsg(0x2A0), ethVehicleStateMsg(0x510)</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>VAL_SCENARIO_CTRL, CHS_GW</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>CHS_GW, ADAS_WARN_CTRL</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>CAN + Ethernet(UDP)</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>속도/주행상태 입력 갱신</t>
+        </is>
+      </c>
+    </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>통신 상세 추적 표 (Comm/Flow/Func/Req)</t>
-        </is>
-      </c>
-    </row>
-    <row r="161"/>
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>Comm_002</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>Flow_002</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>Func_011, Func_012</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>Req_011, Req_012</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>frmSteeringCanMsg(0x2A1), ethSteeringMsg(0x511)</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>VAL_SCENARIO_CTRL, CHS_GW</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>CHS_GW, ADAS_WARN_CTRL</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>CAN + Ethernet(UDP)</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>조향 입력 갱신</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>Comm_003</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>Flow_003</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>Func_007, Func_010</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>Req_007, Req_010</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>frmNavContextCanMsg(0x2A3), ethNavContextMsg(0x512)</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>VAL_SCENARIO_CTRL, INFOTAINMENT_GW</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>INFOTAINMENT_GW, NAV_CTX_MGR, ADAS_WARN_CTRL, WARN_ARB_MGR</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>CAN + Ethernet(UDP)</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>구간/방향/거리/제한속도 입력 갱신</t>
+        </is>
+      </c>
+    </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>Comm ID</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>Flow ID</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
-        <is>
-          <t>Func ID</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>Req ID</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr">
-        <is>
-          <t>Message(ID)</t>
-        </is>
-      </c>
-      <c r="F162" s="3" t="inlineStr">
-        <is>
-          <t>Tx Node</t>
-        </is>
-      </c>
-      <c r="G162" s="3" t="inlineStr">
-        <is>
-          <t>Rx Node</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>Protocol</t>
-        </is>
-      </c>
-      <c r="I162" s="3" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>Clear/비고</t>
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>Comm_004</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Flow_004</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>Func_017</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>Req_017</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>ETH_EmergencyAlert(0xE100)</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>EMS_ALERT(Tx:Police)</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>EMS_ALERT(Rx)</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>Ethernet(UDP)</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>100ms</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>alertState=Clear 또는 송신 중지</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Comm_001</t>
+          <t>Comm_005</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Flow_001</t>
+          <t>Flow_005</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Func_001, Func_002, Func_003, Func_004, Func_006, Func_010</t>
+          <t>Func_018</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Req_001, Req_002, Req_003, Req_004, Req_006, Req_010</t>
+          <t>Req_017</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>frmVehicleStateCanMsg(0x2A0), ethVehicleStateMsg(0x510)</t>
+          <t>ETH_EmergencyAlert(0xE100)</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>VAL_SCENARIO_CTRL, CHS_GW</t>
+          <t>EMS_ALERT(Tx:Ambulance)</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>CHS_GW, ADAS_WARN_CTRL</t>
+          <t>EMS_ALERT(Rx)</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>CAN + Ethernet(UDP)</t>
+          <t>Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
@@ -31127,252 +30587,252 @@
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>속도/주행상태 입력 갱신</t>
+          <t>alertState=Clear 또는 송신 중지</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>Comm_002</t>
+          <t>Comm_006</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Flow_002</t>
+          <t>Flow_006</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Func_011, Func_012</t>
+          <t>Func_022, Func_023, Func_024, Func_025, Func_027, Func_028, Func_029, Func_030, Func_031, Func_032, Func_144, Func_149, Func_150, Func_152</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Req_011, Req_012</t>
+          <t>Req_022, Req_023, Req_024, Req_025, Req_027, Req_028, Req_029, Req_030, Req_031, Req_032, Req_144, Req_149, Req_150, Req_152</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>frmSteeringCanMsg(0x2A1), ethSteeringMsg(0x511)</t>
+          <t>ETH_EmergencyAlert(0xE100), ethSelectedAlertMsg(0xE200)</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>VAL_SCENARIO_CTRL, CHS_GW</t>
+          <t>EMS_ALERT(Rx), WARN_ARB_MGR</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>CHS_GW, ADAS_WARN_CTRL</t>
+          <t>WARN_ARB_MGR, BODY_GW, IVI_GW</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>CAN + Ethernet(UDP)</t>
+          <t>Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>Event + 50ms</t>
         </is>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>조향 입력 갱신</t>
+          <t>1000ms 무갱신 시 timeoutClear=1</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Comm_003</t>
+          <t>Comm_007</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Flow_003</t>
+          <t>Flow_007</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Func_007, Func_010</t>
+          <t>Func_008, Func_009, Func_013, Func_014, Func_015, Func_016, Func_033, Func_034, Func_035, Func_036, Func_037, Func_038, Func_039, Func_152</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Req_007, Req_010</t>
+          <t>Req_008, Req_009, Req_013, Req_014, Req_015, Req_016, Req_033, Req_034, Req_035, Req_037, Req_152</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>frmNavContextCanMsg(0x2A3), ethNavContextMsg(0x512)</t>
+          <t>ethSelectedAlertMsg(0xE200), frmAmbientControlMsg(0x260)</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>VAL_SCENARIO_CTRL, INFOTAINMENT_GW</t>
+          <t>WARN_ARB_MGR, BODY_GW</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>INFOTAINMENT_GW, NAV_CTX_MGR, ADAS_WARN_CTRL, WARN_ARB_MGR</t>
+          <t>BODY_GW, AMBIENT_CTRL</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>CAN + Ethernet(UDP)</t>
+          <t>Ethernet(UDP) + CAN</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>50ms</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>구간/방향/거리/제한속도 입력 갱신</t>
+          <t>selectedAlertLevel/selectedAlertType 수신</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Comm_004</t>
+          <t>Comm_008</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Flow_004</t>
+          <t>Flow_008</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Func_017</t>
+          <t>Func_005, Func_019, Func_020, Func_021, Func_026, Func_040, Func_143, Func_152, Func_155</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Req_017</t>
+          <t>Req_005, Req_019, Req_020, Req_021, Req_026, Req_040, Req_143, Req_152, Req_155</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>ETH_EmergencyAlert(0xE100)</t>
+          <t>ethSelectedAlertMsg(0xE200), frmClusterWarningMsg(0x280)</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT(Tx:Police)</t>
+          <t>WARN_ARB_MGR, IVI_GW</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT(Rx)</t>
+          <t>IVI_GW, CLU_HMI_CTRL</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP)</t>
+          <t>Ethernet(UDP) + CAN</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>50ms</t>
         </is>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>alertState=Clear 또는 송신 중지</t>
+          <t>selectedAlertLevel/selectedAlertType 수신</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Comm_005</t>
+          <t>Comm_009</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Flow_005</t>
+          <t>Flow_009</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Func_018</t>
+          <t>Func_041, Func_042, Func_043</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Req_017</t>
+          <t>Req_041, Req_042, Req_043</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>ETH_EmergencyAlert(0xE100)</t>
+          <t>frmTestResultMsg(0x2A5)</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT(Tx:Ambulance)</t>
+          <t>VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT(Rx)</t>
+          <t>VAL_SCENARIO_CTRL(Log/Panel)</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP)</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>alertState=Clear 또는 송신 중지</t>
+          <t>판정 결과 기록 완료 시 종료</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>Comm_006</t>
+          <t>Comm_120</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Flow_006</t>
+          <t>Flow_120</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Func_022, Func_023, Func_024, Func_025, Func_027, Func_028, Func_029, Func_030, Func_031, Func_032, Func_144, Func_149, Func_150, Func_152</t>
+          <t>Func_120</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Req_022, Req_023, Req_024, Req_025, Req_027, Req_028, Req_029, Req_030, Req_031, Req_032, Req_144, Req_149, Req_150, Req_152</t>
+          <t>Req_120</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>ETH_EmergencyAlert(0xE100), ethSelectedAlertMsg(0xE200)</t>
+          <t>ethEmergencyRiskMsg(0x1C3)</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT(Rx), WARN_ARB_MGR</t>
+          <t>ADAS_WARN_CTRL</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR, BODY_GW, IVI_GW</t>
+          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -31382,49 +30842,49 @@
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>Event + 50ms</t>
+          <t>100ms</t>
         </is>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>1000ms 무갱신 시 timeoutClear=1</t>
+          <t>근접위험 산정 프레임</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Comm_007</t>
+          <t>Comm_121</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Flow_007</t>
+          <t>Flow_121</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Func_008, Func_009, Func_013, Func_014, Func_015, Func_016, Func_033, Func_034, Func_035, Func_036, Func_037, Func_038, Func_039, Func_152</t>
+          <t>Func_121</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Req_008, Req_009, Req_013, Req_014, Req_015, Req_016, Req_033, Req_034, Req_035, Req_037, Req_152</t>
+          <t>Req_121</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>ethSelectedAlertMsg(0xE200), frmAmbientControlMsg(0x260)</t>
+          <t>ethDecelAssistReqMsg(0x1C4)</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR, BODY_GW</t>
+          <t>WARN_ARB_MGR</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>BODY_GW, AMBIENT_CTRL</t>
+          <t>CHS_GW, BRK_CTRL, VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -31434,49 +30894,49 @@
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>50ms</t>
+          <t>Event + 50ms</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>selectedAlertLevel/selectedAlertType 수신</t>
+          <t>감속 보조 요청 프레임</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>Comm_008</t>
+          <t>Comm_122</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Flow_008</t>
+          <t>Flow_122</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Func_005, Func_019, Func_020, Func_021, Func_026, Func_040, Func_143, Func_152, Func_155</t>
+          <t>Func_125, Func_126</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Req_005, Req_019, Req_020, Req_021, Req_026, Req_040, Req_143, Req_152, Req_155</t>
+          <t>Req_125, Req_126</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>ethSelectedAlertMsg(0xE200), frmClusterWarningMsg(0x280)</t>
+          <t>ethSelectedAlertMsg(0xE200), frmAmbientControlMsg(0x260), frmClusterWarningMsg(0x280)</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR, IVI_GW</t>
+          <t>WARN_ARB_MGR</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>IVI_GW, CLU_HMI_CTRL</t>
+          <t>BODY_GW, IVI_GW, AMBIENT_CTRL, CLU_HMI_CTRL</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -31491,662 +30951,358 @@
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t>selectedAlertLevel/selectedAlertType 수신</t>
+          <t>감속 보조 활성 경고 동기화</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Comm_009</t>
+          <t>Comm_123</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Flow_009</t>
+          <t>Flow_123</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Func_041, Func_042, Func_043</t>
+          <t>Func_123</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Req_041, Req_042, Req_043</t>
+          <t>Req_123</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>frmTestResultMsg(0x2A5)</t>
+          <t>frmPedalInputCanMsg(0x2A2), frmSteeringCanMsg(0x2A1), ethDecelAssistReqMsg(0x1C4)</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>VAL_SCENARIO_CTRL</t>
+          <t>CHS_GW, WARN_ARB_MGR</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>VAL_SCENARIO_CTRL(Log/Panel)</t>
+          <t>WARN_ARB_MGR, DOMAIN_ROUTER, BRK_CTRL</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CAN + Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Event + 100ms</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>판정 결과 기록 완료 시 종료</t>
+          <t>운전자 개입 시 보조 해제</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>Comm_120</t>
+          <t>Comm_124</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Flow_120</t>
+          <t>Flow_124</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Func_120</t>
+          <t>Func_127, Func_128, Func_129, Func_151, Func_152</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Req_120</t>
+          <t>Req_127, Req_128, Req_129, Req_151, Req_152</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>ethEmergencyRiskMsg(0x1C3)</t>
+          <t>frmChassisHealthMsg(0x103), frmBodyHealthMsg(0x269), frmInfotainmentHealthMsg(0x288), ethFailSafeStateMsg(0x111)</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>ADAS_WARN_CTRL</t>
+          <t>CHS_GW, BODY_GW, INFOTAINMENT_GW, DOMAIN_BOUNDARY_MGR</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
+          <t>DOMAIN_BOUNDARY_MGR, DOMAIN_ROUTER, WARN_ARB_MGR, BODY_GW, IVI_GW, VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP)</t>
+          <t>CAN + Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>100ms</t>
+          <t>100ms + Event</t>
         </is>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t>근접위험 산정 프레임</t>
+          <t>경로 단절 강등/보조 금지</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>Comm_121</t>
+          <t>Comm_130</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Flow_121</t>
+          <t>Flow_130</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Func_121</t>
+          <t>Func_130, Func_131, Func_148</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Req_121</t>
+          <t>Req_130, Req_131, Req_148</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>ethDecelAssistReqMsg(0x1C4)</t>
+          <t>ethObjectRiskInputMsg(0xE213)</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR</t>
+          <t>CHS_GW, INFOTAINMENT_GW</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>CHS_GW, BRK_CTRL, VAL_SCENARIO_CTRL</t>
+          <t>ADAS_WARN_CTRL</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP) + CAN</t>
+          <t>Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>Event + 50ms</t>
+          <t>100ms</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>감속 보조 요청 프레임</t>
+          <t>객체 목록/대표 위험 후보 입력 (Pre-Activation)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>Comm_122</t>
+          <t>Comm_131</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Flow_122</t>
+          <t>Flow_131</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Func_125, Func_126</t>
+          <t>Func_132, Func_133, Func_136</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Req_125, Req_126</t>
+          <t>Req_132, Req_133, Req_136</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>ethSelectedAlertMsg(0xE200), frmAmbientControlMsg(0x260), frmClusterWarningMsg(0x280)</t>
+          <t>ethObjectRiskStateMsg(0xE214)</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR</t>
+          <t>ADAS_WARN_CTRL</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>BODY_GW, IVI_GW, AMBIENT_CTRL, CLU_HMI_CTRL</t>
+          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>Ethernet(UDP) + CAN</t>
+          <t>Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>50ms</t>
+          <t>100ms + Event</t>
         </is>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>감속 보조 활성 경고 동기화</t>
+          <t>TTC/상대속도/거리 기반 위험 상태 (Pre-Activation)</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Comm_123</t>
+          <t>Comm_132</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Flow_123</t>
+          <t>Flow_132</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Func_123</t>
+          <t>Func_134, Func_135, Func_139</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Req_123</t>
+          <t>Req_134, Req_135, Req_139</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>frmPedalInputCanMsg(0x2A2), frmSteeringCanMsg(0x2A1), ethDecelAssistReqMsg(0x1C4)</t>
+          <t>ethObjectScenarioAlertMsg(0xE215), frmAmbientControlMsg(0x260), frmClusterWarningMsg(0x280)</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>CHS_GW, WARN_ARB_MGR</t>
+          <t>WARN_ARB_MGR</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>WARN_ARB_MGR, DOMAIN_ROUTER, BRK_CTRL</t>
+          <t>BODY_GW, IVI_GW, AMBIENT_CTRL, CLU_HMI_CTRL</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>CAN + Ethernet(UDP)</t>
+          <t>Ethernet(UDP) + CAN</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>Event + 100ms</t>
+          <t>Event + 50ms</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>운전자 개입 시 보조 해제</t>
+          <t>교차로/합류 객체 경고 및 우선순위 정합 (Pre-Activation)</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Comm_124</t>
+          <t>Comm_133</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Flow_124</t>
+          <t>Flow_133</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Func_127, Func_128, Func_129, Func_151, Func_152</t>
+          <t>Func_137, Func_138, Func_148</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Req_127, Req_128, Req_129, Req_151, Req_152</t>
+          <t>Req_137, Req_138, Req_148</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>frmChassisHealthMsg(0x103), frmBodyHealthMsg(0x269), frmInfotainmentHealthMsg(0x288), ethFailSafeStateMsg(0x111)</t>
+          <t>ethObjectSafetyStateMsg(0xE216)</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>CHS_GW, BODY_GW, INFOTAINMENT_GW, DOMAIN_BOUNDARY_MGR</t>
+          <t>DOMAIN_BOUNDARY_MGR, EMS_ALERT</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>DOMAIN_BOUNDARY_MGR, DOMAIN_ROUTER, WARN_ARB_MGR, BODY_GW, IVI_GW, VAL_SCENARIO_CTRL</t>
+          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>CAN + Ethernet(UDP)</t>
+          <t>Ethernet(UDP)</t>
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>100ms + Event</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t>경로 단절 강등/보조 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>Comm_130</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>Flow_130</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>Func_130, Func_131, Func_148</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr">
-        <is>
-          <t>Req_130, Req_131, Req_148</t>
-        </is>
-      </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>ethObjectRiskInputMsg(0xE213)</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>CHS_GW, INFOTAINMENT_GW</t>
-        </is>
-      </c>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>ADAS_WARN_CTRL</t>
-        </is>
-      </c>
-      <c r="H177" s="4" t="inlineStr">
-        <is>
-          <t>Ethernet(UDP)</t>
-        </is>
-      </c>
-      <c r="I177" s="4" t="inlineStr">
-        <is>
-          <t>100ms</t>
-        </is>
-      </c>
-      <c r="J177" s="4" t="inlineStr">
-        <is>
-          <t>객체 목록/대표 위험 후보 입력 (Pre-Activation, ETH 계약 v1.2 대기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>Comm_131</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>Flow_131</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>Func_132, Func_133, Func_136</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr">
-        <is>
-          <t>Req_132, Req_133, Req_136</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>ethObjectRiskStateMsg(0xE214)</t>
-        </is>
-      </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>ADAS_WARN_CTRL</t>
-        </is>
-      </c>
-      <c r="G178" s="4" t="inlineStr">
-        <is>
-          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
-        </is>
-      </c>
-      <c r="H178" s="4" t="inlineStr">
-        <is>
-          <t>Ethernet(UDP)</t>
-        </is>
-      </c>
-      <c r="I178" s="4" t="inlineStr">
-        <is>
-          <t>100ms + Event</t>
-        </is>
-      </c>
-      <c r="J178" s="4" t="inlineStr">
-        <is>
-          <t>TTC/상대속도/거리 기반 위험 상태 (Pre-Activation, ETH 계약 v1.2 대기)</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>Comm_132</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>Flow_132</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>Func_134, Func_135, Func_139</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>Req_134, Req_135, Req_139</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>ethObjectScenarioAlertMsg(0xE215), frmAmbientControlMsg(0x260), frmClusterWarningMsg(0x280)</t>
-        </is>
-      </c>
-      <c r="F179" s="4" t="inlineStr">
-        <is>
-          <t>WARN_ARB_MGR</t>
-        </is>
-      </c>
-      <c r="G179" s="4" t="inlineStr">
-        <is>
-          <t>BODY_GW, IVI_GW, AMBIENT_CTRL, CLU_HMI_CTRL</t>
-        </is>
-      </c>
-      <c r="H179" s="4" t="inlineStr">
-        <is>
-          <t>Ethernet(UDP) + CAN</t>
-        </is>
-      </c>
-      <c r="I179" s="4" t="inlineStr">
-        <is>
-          <t>Event + 50ms</t>
-        </is>
-      </c>
-      <c r="J179" s="4" t="inlineStr">
-        <is>
-          <t>교차로/합류 객체 경고 및 우선순위 정합 (Pre-Activation, ETH 계약 v1.2 대기)</t>
-        </is>
-      </c>
-    </row>
+          <t>신뢰도 강등 및 객체 이벤트 기록 (Pre-Activation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
     <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>Comm_133</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>Flow_133</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>Func_137, Func_138, Func_148</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>Req_137, Req_138, Req_148</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>ethObjectSafetyStateMsg(0xE216)</t>
-        </is>
-      </c>
-      <c r="F180" s="4" t="inlineStr">
-        <is>
-          <t>DOMAIN_BOUNDARY_MGR, EMS_ALERT</t>
-        </is>
-      </c>
-      <c r="G180" s="4" t="inlineStr">
-        <is>
-          <t>WARN_ARB_MGR, VAL_SCENARIO_CTRL</t>
-        </is>
-      </c>
-      <c r="H180" s="4" t="inlineStr">
-        <is>
-          <t>Ethernet(UDP)</t>
-        </is>
-      </c>
-      <c r="I180" s="4" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="J180" s="4" t="inlineStr">
-        <is>
-          <t>신뢰도 강등 및 객체 이벤트 기록 (Pre-Activation, ETH 계약 v1.2 대기)</t>
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>제출본 운용 메모</t>
         </is>
       </c>
     </row>
     <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>- 상단 공식 통신 표와 통신 상세 추적 표를 제출 기준 본표로 유지한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>- Baseline(Comm_101~106, 201~205)은 Defined, V2(Comm_120~124)는 Implemented 상태로 관리한다.</t>
+        </is>
+      </c>
+    </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>하단 확장표 축소 (제출본)</t>
-        </is>
-      </c>
-    </row>
-    <row r="185"/>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>- 상단 공식 통신 표와 통신 상세 추적 표를 제출 기준 본표로 유지한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>- 도메인별 Comm 확장 전수표는 중복을 줄이기 위해 요약만 유지한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>- 상세 전수 매핑은 원문 SoT(driving-situation-alert/0303_Communication_Specification.md)를 기준으로 관리한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="189"/>
-    <row r="190">
-      <c r="A190" s="3" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>제출본 유지 내용</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="inlineStr">
-        <is>
-          <t>원문 SoT 참조</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>도메인별 통신 원본</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>Domain CAN/ETH 논리 계약 분리 원칙 요약</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr">
-        <is>
-          <t>0303 원문 `도메인별 통신 원본 확장 정의`</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>Vehicle Baseline 확장</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>Comm_101~106, Comm_201~205 `Defined` 상태 유지</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>0303 원문 Baseline/Phase-B 확장 표</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>V2 확장</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>Comm_120~124 `Implemented` 상태 유지</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>0303 원문 V2 확장 표</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>ADAS 객체 인지 확장</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>Comm_130~133 `Planned(Pre-Activation)` 유지</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>0303 원문 ADAS 확장 표</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>활성 승격 조건</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>`ETH_INTERFACE_CONTRACT.md v1.2`의 `E213~E216` 반영 시 활성</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>0303 원문 ADAS 확장 섹션</t>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>- ADAS 객체 확장(Comm_130~133)은 Planned(Pre-Activation) 상태로 유지한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>- 상세 전수 매핑과 도메인 분해표는 원문 SoT(driving-situation-alert/0303_Communication_Specification.md)를 기준으로 관리한다.</t>
         </is>
       </c>
     </row>
@@ -44813,7 +43969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -47221,7 +46377,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>EMS 논리 단말-내부 모듈 매핑</t>
+          <t>경고 표시 정책표 요약 (Req_008, Req_035, Req_037)</t>
         </is>
       </c>
     </row>
@@ -47229,66 +46385,307 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>논리 단말(문서 표준)</t>
+          <t>selectedAlertType</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>내부 구현 모듈(코드/통신)</t>
+          <t>의미</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>ambientMode</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>ambientColor</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>ambientPattern</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>EMS_POLICE_TX</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>경찰 긴급 알림 송신</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>EMS_ALERT</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>EMS_AMB_TX</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>구급 긴급 알림 송신</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>1/5 교차</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Ambulance</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>1/6 교차</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>School Zone</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Highway (무조향 의심)</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Guide Left</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Guide Right</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>- warningTextCode 정책: timeoutClear == 0 이고 selectedAlertLevel &gt; 0이면 selectedAlertType*10 + selectedAlertLevel, 그 외는 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>- 상세 코드 사전(ambientColor, ambientPattern, ambientMode)은 원문 SoT 03_Function_definition.md를 기준으로 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139"/>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>EMS 논리 단말-내부 모듈 매핑</t>
+        </is>
+      </c>
+    </row>
+    <row r="141"/>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>논리 단말(문서 표준)</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>내부 구현 모듈(코드/통신)</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
           <t>EMS_ALERT</t>
         </is>
       </c>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>EMS_POLICE_TX</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>경찰 긴급 알림 송신</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>EMS_ALERT</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>EMS_AMB_TX</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>구급 긴급 알림 송신</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>EMS_ALERT</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>EMS_ALERT_RX</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
         <is>
           <t>긴급 알림 수신/해제/타임아웃 처리</t>
         </is>
